--- a/source_data/workbooks/Source_Data_Fig5.xlsx
+++ b/source_data/workbooks/Source_Data_Fig5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="127">
   <si>
     <t>plot_order</t>
   </si>
@@ -103,7 +103,7 @@
     <t>30 min</t>
   </si>
   <si>
-    <t>reference</t>
+    <t>Ground truth</t>
   </si>
   <si>
     <t>predicted tumour cell count</t>
@@ -121,6 +121,30 @@
     <t>accuracy of the answer</t>
   </si>
   <si>
+    <t>Figure 5f</t>
+  </si>
+  <si>
+    <t>Neoplastic cell quantification</t>
+  </si>
+  <si>
+    <t>Initial iteration</t>
+  </si>
+  <si>
+    <t>Iteration t=30</t>
+  </si>
+  <si>
+    <t>answer (cells)</t>
+  </si>
+  <si>
+    <t>IoU with reference cells</t>
+  </si>
+  <si>
+    <t>n.a. one evaluation</t>
+  </si>
+  <si>
+    <t>n.a. single specimen</t>
+  </si>
+  <si>
     <t>run1</t>
   </si>
   <si>
@@ -136,10 +160,13 @@
     <t>run5</t>
   </si>
   <si>
-    <t>Figure 5f</t>
-  </si>
-  <si>
-    <t>Neoplastic cell quantification</t>
+    <t>Figure 5g</t>
+  </si>
+  <si>
+    <t>Tumour to normal duct ratio</t>
+  </si>
+  <si>
+    <t>Visium HD prostate, one section</t>
   </si>
   <si>
     <t>LLaVA-Med</t>
@@ -169,78 +196,21 @@
     <t>NOVA</t>
   </si>
   <si>
-    <t>TLAgent-removing knowledge</t>
-  </si>
-  <si>
-    <t>TLAgent</t>
+    <t>TissueLab</t>
   </si>
   <si>
     <t>answer</t>
   </si>
   <si>
-    <t>answer (cells)</t>
+    <t>answer (per cent)</t>
+  </si>
+  <si>
+    <t>reference (per cent)</t>
   </si>
   <si>
     <t>no evaluable output</t>
   </si>
   <si>
-    <t>0.0038</t>
-  </si>
-  <si>
-    <t>319.0</t>
-  </si>
-  <si>
-    <t>0.0001</t>
-  </si>
-  <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>0.0145</t>
-  </si>
-  <si>
-    <t>1234.0</t>
-  </si>
-  <si>
-    <t>0.0294</t>
-  </si>
-  <si>
-    <t>2502.2</t>
-  </si>
-  <si>
-    <t>0.0003</t>
-  </si>
-  <si>
-    <t>24.0</t>
-  </si>
-  <si>
-    <t>0.9487</t>
-  </si>
-  <si>
-    <t>89379.0</t>
-  </si>
-  <si>
-    <t>85014.0</t>
-  </si>
-  <si>
-    <t>n.a. single specimen</t>
-  </si>
-  <si>
-    <t>Figure 5g</t>
-  </si>
-  <si>
-    <t>Tumour to normal duct ratio</t>
-  </si>
-  <si>
-    <t>Visium HD prostate, one section</t>
-  </si>
-  <si>
-    <t>answer (per cent)</t>
-  </si>
-  <si>
-    <t>reference (per cent)</t>
-  </si>
-  <si>
     <t>0.0623</t>
   </si>
   <si>
@@ -281,12 +251,6 @@
   </si>
   <si>
     <t>1.2911</t>
-  </si>
-  <si>
-    <t>0.0326</t>
-  </si>
-  <si>
-    <t>0.07</t>
   </si>
   <si>
     <t>0.9981</t>
@@ -775,7 +739,7 @@
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="59.7109375" customWidth="1"/>
     <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="29.7109375" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -1492,26 +1456,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="32.7109375" customWidth="1"/>
     <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="6" max="6" width="26.7109375" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
     <col min="9" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="11" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="21.7109375" customWidth="1"/>
     <col min="14" max="17" width="22.7109375" customWidth="1"/>
-    <col min="18" max="22" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1563,40 +1525,25 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>33</v>
       </c>
-      <c r="S1" t="s">
+      <c r="C2" t="s">
         <v>34</v>
-      </c>
-      <c r="T1" t="s">
-        <v>35</v>
-      </c>
-      <c r="U1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
@@ -1608,33 +1555,48 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0.0527</v>
+      </c>
+      <c r="M2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
         <v>30</v>
@@ -1646,33 +1608,48 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0.9487</v>
+      </c>
+      <c r="M3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G4" t="s">
         <v>30</v>
@@ -1684,33 +1661,48 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>4478</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
@@ -1722,33 +1714,48 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>89379</v>
+      </c>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -1760,33 +1767,48 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0.1012</v>
+      </c>
+      <c r="M6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
@@ -1798,63 +1820,48 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>5</v>
-      </c>
-      <c r="L7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7">
-        <v>0.0069</v>
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0.889</v>
+      </c>
+      <c r="M7" t="s">
+        <v>39</v>
       </c>
       <c r="N7" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O7" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P7" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q7" t="s">
-        <v>67</v>
-      </c>
-      <c r="R7">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="S7">
-        <v>0.0008</v>
-      </c>
-      <c r="T7">
-        <v>0.0007</v>
-      </c>
-      <c r="U7">
-        <v>0.0005</v>
-      </c>
-      <c r="V7">
-        <v>0.0161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
@@ -1865,756 +1872,8 @@
       <c r="I8">
         <v>1</v>
       </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-      <c r="K8">
-        <v>5</v>
-      </c>
-      <c r="L8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8">
-        <v>584.8012</v>
-      </c>
-      <c r="N8" t="s">
-        <v>67</v>
-      </c>
-      <c r="O8" t="s">
-        <v>67</v>
-      </c>
-      <c r="P8" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>67</v>
-      </c>
-      <c r="R8">
-        <v>55</v>
-      </c>
-      <c r="S8">
-        <v>70</v>
-      </c>
-      <c r="T8">
-        <v>60</v>
-      </c>
-      <c r="U8">
-        <v>45</v>
-      </c>
-      <c r="V8">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
-      </c>
-      <c r="K9">
-        <v>5</v>
-      </c>
-      <c r="L9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M9">
-        <v>0.0001</v>
-      </c>
-      <c r="N9" t="s">
-        <v>67</v>
-      </c>
-      <c r="O9" t="s">
-        <v>67</v>
-      </c>
-      <c r="P9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>67</v>
-      </c>
-      <c r="R9">
-        <v>0.0003</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0.0001</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>5</v>
-      </c>
-      <c r="K10">
-        <v>5</v>
-      </c>
-      <c r="L10" t="s">
-        <v>57</v>
-      </c>
-      <c r="M10">
-        <v>10.2713</v>
-      </c>
-      <c r="N10" t="s">
-        <v>67</v>
-      </c>
-      <c r="O10" t="s">
-        <v>67</v>
-      </c>
-      <c r="P10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>67</v>
-      </c>
-      <c r="R10">
-        <v>25</v>
-      </c>
-      <c r="S10">
-        <v>4</v>
-      </c>
-      <c r="T10">
-        <v>5</v>
-      </c>
-      <c r="U10">
-        <v>1</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>5</v>
-      </c>
-      <c r="K11">
-        <v>5</v>
-      </c>
-      <c r="L11" t="s">
-        <v>58</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>67</v>
-      </c>
-      <c r="O11" t="s">
-        <v>67</v>
-      </c>
-      <c r="P11" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>67</v>
-      </c>
-      <c r="R11">
-        <v>0.0145</v>
-      </c>
-      <c r="S11">
-        <v>0.0145</v>
-      </c>
-      <c r="T11">
-        <v>0.0145</v>
-      </c>
-      <c r="U11">
-        <v>0.0145</v>
-      </c>
-      <c r="V11">
-        <v>0.0145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>5</v>
-      </c>
-      <c r="K12">
-        <v>5</v>
-      </c>
-      <c r="L12" t="s">
-        <v>59</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>67</v>
-      </c>
-      <c r="O12" t="s">
-        <v>67</v>
-      </c>
-      <c r="P12" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>67</v>
-      </c>
-      <c r="R12">
-        <v>1234</v>
-      </c>
-      <c r="S12">
-        <v>1234</v>
-      </c>
-      <c r="T12">
-        <v>1234</v>
-      </c>
-      <c r="U12">
-        <v>1234</v>
-      </c>
-      <c r="V12">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>5</v>
-      </c>
-      <c r="K13">
-        <v>5</v>
-      </c>
-      <c r="L13" t="s">
-        <v>60</v>
-      </c>
-      <c r="M13">
-        <v>0.0369</v>
-      </c>
-      <c r="N13" t="s">
-        <v>67</v>
-      </c>
-      <c r="O13" t="s">
-        <v>67</v>
-      </c>
-      <c r="P13" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>67</v>
-      </c>
-      <c r="R13">
-        <v>0.0617</v>
-      </c>
-      <c r="S13">
-        <v>0.0054</v>
-      </c>
-      <c r="T13">
-        <v>0.0026</v>
-      </c>
-      <c r="U13">
-        <v>0.0004</v>
-      </c>
-      <c r="V13">
-        <v>0.0771</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>5</v>
-      </c>
-      <c r="K14">
-        <v>5</v>
-      </c>
-      <c r="L14" t="s">
-        <v>61</v>
-      </c>
-      <c r="M14">
-        <v>3139.4677</v>
-      </c>
-      <c r="N14" t="s">
-        <v>67</v>
-      </c>
-      <c r="O14" t="s">
-        <v>67</v>
-      </c>
-      <c r="P14" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>67</v>
-      </c>
-      <c r="R14">
-        <v>5248</v>
-      </c>
-      <c r="S14">
-        <v>460</v>
-      </c>
-      <c r="T14">
-        <v>217</v>
-      </c>
-      <c r="U14">
-        <v>34</v>
-      </c>
-      <c r="V14">
-        <v>6552</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>5</v>
-      </c>
-      <c r="K15">
-        <v>5</v>
-      </c>
-      <c r="L15" t="s">
-        <v>62</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>67</v>
-      </c>
-      <c r="O15" t="s">
-        <v>67</v>
-      </c>
-      <c r="P15" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>67</v>
-      </c>
-      <c r="R15">
-        <v>0.0003</v>
-      </c>
-      <c r="S15">
-        <v>0.0003</v>
-      </c>
-      <c r="T15">
-        <v>0.0003</v>
-      </c>
-      <c r="U15">
-        <v>0.0003</v>
-      </c>
-      <c r="V15">
-        <v>0.0003</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>5</v>
-      </c>
-      <c r="K16">
-        <v>5</v>
-      </c>
-      <c r="L16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>67</v>
-      </c>
-      <c r="O16" t="s">
-        <v>67</v>
-      </c>
-      <c r="P16" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>67</v>
-      </c>
-      <c r="R16">
-        <v>24</v>
-      </c>
-      <c r="S16">
-        <v>24</v>
-      </c>
-      <c r="T16">
-        <v>24</v>
-      </c>
-      <c r="U16">
-        <v>24</v>
-      </c>
-      <c r="V16">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>5</v>
-      </c>
-      <c r="K17">
-        <v>5</v>
-      </c>
-      <c r="L17" t="s">
-        <v>64</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>67</v>
-      </c>
-      <c r="O17" t="s">
-        <v>67</v>
-      </c>
-      <c r="P17" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>67</v>
-      </c>
-      <c r="R17">
-        <v>0.9487</v>
-      </c>
-      <c r="S17">
-        <v>0.9487</v>
-      </c>
-      <c r="T17">
-        <v>0.9487</v>
-      </c>
-      <c r="U17">
-        <v>0.9487</v>
-      </c>
-      <c r="V17">
-        <v>0.9487</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>5</v>
-      </c>
-      <c r="K18">
-        <v>5</v>
-      </c>
-      <c r="L18" t="s">
-        <v>65</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>67</v>
-      </c>
-      <c r="O18" t="s">
-        <v>67</v>
-      </c>
-      <c r="P18" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>67</v>
-      </c>
-      <c r="R18">
-        <v>89379</v>
-      </c>
-      <c r="S18">
-        <v>89379</v>
-      </c>
-      <c r="T18">
-        <v>89379</v>
-      </c>
-      <c r="U18">
-        <v>89379</v>
-      </c>
-      <c r="V18">
-        <v>89379</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="L19" t="s">
-        <v>66</v>
+      <c r="L8">
+        <v>85014</v>
       </c>
     </row>
   </sheetData>
@@ -2624,14 +1883,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" customWidth="1"/>
     <col min="4" max="4" width="33.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.7109375" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -2696,19 +1955,19 @@
         <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="S1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="T1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="U1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="V1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -2716,19 +1975,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
@@ -2746,7 +2005,7 @@
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -2754,19 +2013,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G3" t="s">
         <v>30</v>
@@ -2784,7 +2043,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -2792,16 +2051,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
         <v>32</v>
@@ -2822,22 +2081,22 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M4">
-        <v>0.1074</v>
+        <v>0.0833</v>
       </c>
       <c r="N4" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O4" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P4" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q4" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -2854,19 +2113,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
@@ -2884,22 +2143,22 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="M5">
         <v>6.8153</v>
       </c>
       <c r="N5" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O5" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P5" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q5" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R5">
         <v>12</v>
@@ -2916,16 +2175,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
         <v>32</v>
@@ -2946,22 +2205,22 @@
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="M6">
         <v>0.1495</v>
       </c>
       <c r="N6" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O6" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P6" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q6" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R6">
         <v>0.6986</v>
@@ -2984,19 +2243,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
@@ -3014,22 +2273,22 @@
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="M7">
         <v>0.6269</v>
       </c>
       <c r="N7" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O7" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P7" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q7" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R7">
         <v>1.5</v>
@@ -3052,16 +2311,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
         <v>32</v>
@@ -3082,22 +2341,22 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="M8">
-        <v>0.1963</v>
+        <v>0.1809</v>
       </c>
       <c r="N8" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O8" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P8" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -3117,19 +2376,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
         <v>30</v>
@@ -3147,22 +2406,22 @@
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="M9">
         <v>2.1502</v>
       </c>
       <c r="N9" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O9" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P9" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q9" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -3182,16 +2441,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
         <v>32</v>
@@ -3212,22 +2471,22 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="M10">
         <v>0.3001</v>
       </c>
       <c r="N10" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O10" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P10" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q10" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R10">
         <v>0.7423999999999999</v>
@@ -3250,19 +2509,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
         <v>30</v>
@@ -3280,22 +2539,22 @@
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M11">
         <v>1.7734</v>
       </c>
       <c r="N11" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O11" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P11" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q11" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R11">
         <v>2.7</v>
@@ -3318,16 +2577,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
         <v>32</v>
@@ -3348,22 +2607,22 @@
         <v>5</v>
       </c>
       <c r="L12" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O12" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P12" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q12" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3386,19 +2645,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
         <v>30</v>
@@ -3416,19 +2675,19 @@
         <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="N13" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O13" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P13" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q13" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R13">
         <v>1063.32</v>
@@ -3443,7 +2702,7 @@
         <v>832.794</v>
       </c>
       <c r="V13" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3451,16 +2710,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
         <v>32</v>
@@ -3481,22 +2740,22 @@
         <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O14" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P14" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q14" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R14">
         <v>0.7423999999999999</v>
@@ -3519,19 +2778,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
         <v>30</v>
@@ -3549,22 +2808,22 @@
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O15" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P15" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q15" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R15">
         <v>2.7</v>
@@ -3587,16 +2846,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s">
         <v>32</v>
@@ -3617,22 +2876,22 @@
         <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="M16">
         <v>0.3799</v>
       </c>
       <c r="N16" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O16" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P16" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q16" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R16">
         <v>0.9752999999999999</v>
@@ -3655,19 +2914,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G17" t="s">
         <v>30</v>
@@ -3685,22 +2944,22 @@
         <v>5</v>
       </c>
       <c r="L17" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="M17">
         <v>1.0915</v>
       </c>
       <c r="N17" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O17" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P17" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q17" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R17">
         <v>2.2</v>
@@ -3723,16 +2982,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s">
         <v>32</v>
@@ -3753,37 +3012,37 @@
         <v>5</v>
       </c>
       <c r="L18" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O18" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P18" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q18" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R18">
-        <v>0.0326</v>
+        <v>0.9981</v>
       </c>
       <c r="S18">
-        <v>0.0326</v>
+        <v>0.9981</v>
       </c>
       <c r="T18">
-        <v>0.0326</v>
+        <v>0.9981</v>
       </c>
       <c r="U18">
-        <v>0.0326</v>
+        <v>0.9981</v>
       </c>
       <c r="V18">
-        <v>0.0326</v>
+        <v>0.9981</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3791,19 +3050,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G19" t="s">
         <v>30</v>
@@ -3821,37 +3080,37 @@
         <v>5</v>
       </c>
       <c r="L19" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="O19" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P19" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="Q19" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="R19">
-        <v>0.07000000000000001</v>
+        <v>2.151</v>
       </c>
       <c r="S19">
-        <v>0.07000000000000001</v>
+        <v>2.151</v>
       </c>
       <c r="T19">
-        <v>0.07000000000000001</v>
+        <v>2.151</v>
       </c>
       <c r="U19">
-        <v>0.07000000000000001</v>
+        <v>2.151</v>
       </c>
       <c r="V19">
-        <v>0.07000000000000001</v>
+        <v>2.151</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3859,19 +3118,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
         <v>30</v>
@@ -3882,144 +3141,8 @@
       <c r="I20">
         <v>1</v>
       </c>
-      <c r="J20">
-        <v>5</v>
-      </c>
-      <c r="K20">
-        <v>5</v>
-      </c>
       <c r="L20" t="s">
-        <v>89</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>67</v>
-      </c>
-      <c r="O20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P20" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>67</v>
-      </c>
-      <c r="R20">
-        <v>0.9981</v>
-      </c>
-      <c r="S20">
-        <v>0.9981</v>
-      </c>
-      <c r="T20">
-        <v>0.9981</v>
-      </c>
-      <c r="U20">
-        <v>0.9981</v>
-      </c>
-      <c r="V20">
-        <v>0.9981</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21">
-        <v>5</v>
-      </c>
-      <c r="K21">
-        <v>5</v>
-      </c>
-      <c r="L21" t="s">
-        <v>90</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>67</v>
-      </c>
-      <c r="O21" t="s">
-        <v>67</v>
-      </c>
-      <c r="P21" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>67</v>
-      </c>
-      <c r="R21">
-        <v>2.151</v>
-      </c>
-      <c r="S21">
-        <v>2.151</v>
-      </c>
-      <c r="T21">
-        <v>2.151</v>
-      </c>
-      <c r="U21">
-        <v>2.151</v>
-      </c>
-      <c r="V21">
-        <v>2.151</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="L22" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4104,13 +3227,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -4142,16 +3265,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F3" t="s">
         <v>32</v>
@@ -4180,16 +3303,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
         <v>32</v>
@@ -4218,16 +3341,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F5" t="s">
         <v>32</v>
@@ -4256,16 +3379,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
         <v>32</v>
@@ -4294,13 +3417,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
@@ -4332,16 +3455,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
         <v>32</v>
@@ -4370,16 +3493,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
         <v>32</v>
@@ -4408,16 +3531,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F10" t="s">
         <v>32</v>
@@ -4446,16 +3569,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
@@ -4484,13 +3607,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
         <v>24</v>
@@ -4522,16 +3645,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F13" t="s">
         <v>32</v>
@@ -4560,16 +3683,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F14" t="s">
         <v>32</v>
@@ -4675,19 +3798,19 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
         <v>93</v>
       </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>105</v>
-      </c>
       <c r="F2" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
@@ -4713,19 +3836,19 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G3" t="s">
         <v>30</v>
@@ -4751,19 +3874,19 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G4" t="s">
         <v>30</v>
@@ -4789,19 +3912,19 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
@@ -4827,19 +3950,19 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -4865,19 +3988,19 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
@@ -4903,19 +4026,19 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
@@ -4941,19 +4064,19 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G9" t="s">
         <v>30</v>
@@ -4979,19 +4102,19 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G10" t="s">
         <v>30</v>
@@ -5017,19 +4140,19 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s">
         <v>30</v>
@@ -5055,19 +4178,19 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G12" t="s">
         <v>30</v>
@@ -5093,19 +4216,19 @@
         <v>36</v>
       </c>
       <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
         <v>104</v>
       </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" t="s">
-        <v>116</v>
-      </c>
       <c r="F13" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G13" t="s">
         <v>30</v>
@@ -5131,19 +4254,19 @@
         <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F14" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G14" t="s">
         <v>30</v>
@@ -5169,19 +4292,19 @@
         <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F15" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G15" t="s">
         <v>30</v>
@@ -5207,19 +4330,19 @@
         <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F16" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G16" t="s">
         <v>30</v>
@@ -5245,19 +4368,19 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F17" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G17" t="s">
         <v>30</v>
@@ -5283,19 +4406,19 @@
         <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F18" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G18" t="s">
         <v>30</v>
@@ -5321,19 +4444,19 @@
         <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G19" t="s">
         <v>30</v>
@@ -5359,19 +4482,19 @@
         <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" t="s">
         <v>123</v>
-      </c>
-      <c r="F20" t="s">
-        <v>135</v>
       </c>
       <c r="G20" t="s">
         <v>30</v>
@@ -5397,19 +4520,19 @@
         <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F21" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G21" t="s">
         <v>30</v>
@@ -5435,19 +4558,19 @@
         <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G22" t="s">
         <v>30</v>
@@ -5473,19 +4596,19 @@
         <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G23" t="s">
         <v>30</v>
@@ -5511,19 +4634,19 @@
         <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="F24" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G24" t="s">
         <v>30</v>
@@ -5549,19 +4672,19 @@
         <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G25" t="s">
         <v>30</v>
@@ -5587,19 +4710,19 @@
         <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="F26" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G26" t="s">
         <v>30</v>
@@ -5625,19 +4748,19 @@
         <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F27" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G27" t="s">
         <v>30</v>
@@ -5663,19 +4786,19 @@
         <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="F28" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G28" t="s">
         <v>30</v>
@@ -5701,19 +4824,19 @@
         <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F29" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G29" t="s">
         <v>30</v>
@@ -5739,19 +4862,19 @@
         <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F30" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G30" t="s">
         <v>30</v>
@@ -5777,19 +4900,19 @@
         <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G31" t="s">
         <v>30</v>
@@ -5815,19 +4938,19 @@
         <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
       </c>
       <c r="F32" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="G32" t="s">
         <v>30</v>
@@ -5930,19 +5053,19 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
         <v>93</v>
       </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" t="s">
-        <v>105</v>
-      </c>
       <c r="F2" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G2" t="s">
         <v>30</v>
@@ -5968,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G3" t="s">
         <v>30</v>
@@ -6006,19 +5129,19 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G4" t="s">
         <v>30</v>
@@ -6044,19 +5167,19 @@
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G5" t="s">
         <v>30</v>
@@ -6082,19 +5205,19 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -6120,19 +5243,19 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G7" t="s">
         <v>30</v>
@@ -6158,19 +5281,19 @@
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G8" t="s">
         <v>30</v>
@@ -6196,19 +5319,19 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G9" t="s">
         <v>30</v>
@@ -6234,19 +5357,19 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G10" t="s">
         <v>30</v>
@@ -6272,19 +5395,19 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G11" t="s">
         <v>30</v>
@@ -6310,19 +5433,19 @@
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G12" t="s">
         <v>30</v>
@@ -6348,19 +5471,19 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="F13" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G13" t="s">
         <v>30</v>
@@ -6386,19 +5509,19 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F14" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G14" t="s">
         <v>30</v>
@@ -6424,19 +5547,19 @@
         <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F15" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G15" t="s">
         <v>30</v>
@@ -6462,19 +5585,19 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F16" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G16" t="s">
         <v>30</v>
@@ -6500,19 +5623,19 @@
         <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="F17" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G17" t="s">
         <v>30</v>
@@ -6538,19 +5661,19 @@
         <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F18" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G18" t="s">
         <v>30</v>
@@ -6576,19 +5699,19 @@
         <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G19" t="s">
         <v>30</v>
@@ -6614,19 +5737,19 @@
         <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F20" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G20" t="s">
         <v>30</v>
@@ -6652,19 +5775,19 @@
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F21" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G21" t="s">
         <v>30</v>
@@ -6690,19 +5813,19 @@
         <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G22" t="s">
         <v>30</v>
@@ -6728,19 +5851,19 @@
         <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" t="s">
         <v>126</v>
-      </c>
-      <c r="F23" t="s">
-        <v>138</v>
       </c>
       <c r="G23" t="s">
         <v>30</v>
@@ -6766,19 +5889,19 @@
         <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="F24" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G24" t="s">
         <v>30</v>
@@ -6804,19 +5927,19 @@
         <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G25" t="s">
         <v>30</v>
@@ -6842,19 +5965,19 @@
         <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="F26" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G26" t="s">
         <v>30</v>
@@ -6880,19 +6003,19 @@
         <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F27" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G27" t="s">
         <v>30</v>
@@ -6918,19 +6041,19 @@
         <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="F28" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G28" t="s">
         <v>30</v>
@@ -6956,19 +6079,19 @@
         <v>69</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F29" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G29" t="s">
         <v>30</v>
@@ -6994,19 +6117,19 @@
         <v>71</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E30" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F30" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G30" t="s">
         <v>30</v>
@@ -7032,19 +6155,19 @@
         <v>73</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E31" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="G31" t="s">
         <v>30</v>
